--- a/output/tables/mesh/stats-level_glm_level1.xlsx
+++ b/output/tables/mesh/stats-level_glm_level1.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
           <t>mesh_term</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>stats.sign</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -409,6 +414,11 @@
           <t>Eukaryota</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -433,6 +443,11 @@
           <t>Investigative Techniques</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -457,6 +472,11 @@
           <t>Environment and Public Health</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -481,6 +501,11 @@
           <t>Information Science</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -505,6 +530,11 @@
           <t>Health Care Quality, Access, and Evaluation</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -529,6 +559,11 @@
           <t>Diagnosis</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,6 +588,11 @@
           <t>Persons</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -577,6 +617,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -601,6 +646,11 @@
           <t>Mathematical Concepts</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -625,6 +675,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -649,6 +704,11 @@
           <t>Behavior and Behavior Mechanisms</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -673,6 +733,11 @@
           <t>Psychological Phenomena</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -697,6 +762,11 @@
           <t>Natural Science Disciplines</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -721,6 +791,11 @@
           <t>Health Services Administration</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -745,6 +820,11 @@
           <t>Geographic Locations</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -769,6 +849,11 @@
           <t>Health Care Facilities, Manpower, and Services</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -793,6 +878,11 @@
           <t>Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -817,6 +907,11 @@
           <t>Physical Phenomena</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -841,6 +936,11 @@
           <t>Social Sciences</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -865,6 +965,11 @@
           <t>Pathological Conditions, Signs and Symptoms</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -889,6 +994,11 @@
           <t>Therapeutics</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -913,6 +1023,11 @@
           <t>Genetic Phenomena</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -937,6 +1052,11 @@
           <t>Musculoskeletal and Neural Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -961,6 +1081,11 @@
           <t>Technology, Industry, and Agriculture</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -985,6 +1110,11 @@
           <t>Biological Phenomena</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1009,6 +1139,11 @@
           <t>Neoplasms</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1033,6 +1168,11 @@
           <t>Chemical Phenomena</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1057,6 +1197,11 @@
           <t>Amino Acids, Peptides, and Proteins</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1081,6 +1226,11 @@
           <t>Health Occupations</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1105,6 +1255,11 @@
           <t>Nervous System Diseases</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1129,6 +1284,11 @@
           <t>Chemical Actions and Uses</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1153,6 +1313,11 @@
           <t>Nervous System</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1177,6 +1342,11 @@
           <t>Population Characteristics</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1201,6 +1371,11 @@
           <t>Equipment and Supplies</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1225,6 +1400,11 @@
           <t>Health Care Economics and Organizations</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1249,6 +1429,11 @@
           <t>Surgical Procedures, Operative</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1273,6 +1458,11 @@
           <t>Education</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1297,6 +1487,11 @@
           <t>Behavioral Disciplines and Activities</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1321,6 +1516,11 @@
           <t>Cells</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1345,6 +1545,11 @@
           <t>Cardiovascular Diseases</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1369,6 +1574,11 @@
           <t>Humanities</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1393,6 +1603,11 @@
           <t>Mental Disorders</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1417,6 +1632,11 @@
           <t>Human Activities</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1441,6 +1661,11 @@
           <t>Body Regions</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1465,6 +1690,11 @@
           <t>Infections</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1489,6 +1719,11 @@
           <t>Musculoskeletal System</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1513,6 +1748,11 @@
           <t>Respiratory Tract Diseases</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1537,6 +1777,11 @@
           <t>Inorganic Chemicals</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1561,6 +1806,11 @@
           <t>Organic Chemicals</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1585,6 +1835,11 @@
           <t>Biological Factors</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1609,6 +1864,11 @@
           <t>Metabolism</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1633,6 +1893,11 @@
           <t>Cell Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1657,6 +1922,11 @@
           <t>Urogenital Diseases</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1681,6 +1951,11 @@
           <t>Circulatory and Respiratory Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1705,6 +1980,11 @@
           <t>Tissues</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1729,6 +2009,11 @@
           <t>Skin and Connective Tissue Diseases</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1753,6 +2038,11 @@
           <t>Nucleic Acids, Nucleotides, and Nucleosides</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1777,6 +2067,11 @@
           <t>Reproductive and Urinary Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1801,6 +2096,11 @@
           <t>Digestive System Diseases</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1825,6 +2125,11 @@
           <t>Cardiovascular System</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1849,6 +2154,11 @@
           <t>Nutritional and Metabolic Diseases</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1873,6 +2183,11 @@
           <t>Immune System Diseases</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1897,6 +2212,11 @@
           <t>Ocular Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1921,6 +2241,11 @@
           <t>Enzymes and Coenzymes</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1945,6 +2270,11 @@
           <t>Carbohydrates</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1969,6 +2299,11 @@
           <t>Endocrine System Diseases</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1993,6 +2328,11 @@
           <t>Eye Diseases</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2017,6 +2357,11 @@
           <t>Musculoskeletal Diseases</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2041,6 +2386,11 @@
           <t>Viruses</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2065,6 +2415,11 @@
           <t>Heterocyclic Compounds</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2089,6 +2444,11 @@
           <t>Wounds and Injuries</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2113,6 +2473,11 @@
           <t>Sense Organs</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2137,6 +2502,11 @@
           <t>Complex Mixtures</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2161,6 +2531,11 @@
           <t>Bacteria</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2185,6 +2560,11 @@
           <t>Congenital, Hereditary, and Neonatal Diseases and Abnormalities</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2209,6 +2589,11 @@
           <t>Non-Medical Public and Private Facilities</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2233,6 +2618,11 @@
           <t>Food and Beverages</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2257,6 +2647,11 @@
           <t>Pharmaceutical Preparations</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2281,6 +2676,11 @@
           <t>Digestive System</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2305,6 +2705,11 @@
           <t>Macromolecular Substances</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2329,6 +2734,11 @@
           <t>Otorhinolaryngologic Diseases</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2353,6 +2763,11 @@
           <t>Dentistry</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2377,6 +2792,11 @@
           <t>Chemically-Induced Disorders</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2401,6 +2821,11 @@
           <t>Urogenital System</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2425,6 +2850,11 @@
           <t>Biomedical and Dental Materials</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2449,6 +2879,11 @@
           <t>Hemic and Immune Systems</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2473,6 +2908,11 @@
           <t>Stomatognathic System</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2497,6 +2937,11 @@
           <t>Respiratory System</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2521,6 +2966,11 @@
           <t>Stomatognathic Diseases</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2545,6 +2995,11 @@
           <t>Microbiological Phenomena</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2569,6 +3024,11 @@
           <t>Polycyclic Compounds</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2593,6 +3053,11 @@
           <t>Lipids</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2617,6 +3082,11 @@
           <t>Plant Structures</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2641,6 +3111,11 @@
           <t>Hemic and Lymphatic Diseases</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2665,6 +3140,11 @@
           <t>Animal Diseases</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2689,6 +3169,11 @@
           <t>Hormones, Hormone Substitutes, and Hormone Antagonists</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2713,6 +3198,11 @@
           <t>Fluids and Secretions</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2737,6 +3227,11 @@
           <t>Immune System Phenomena</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2761,6 +3256,11 @@
           <t>Integumentary System</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2785,6 +3285,11 @@
           <t>Embryonic Structures</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2809,6 +3314,11 @@
           <t>Organism Forms</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2833,6 +3343,11 @@
           <t>Animal Structures</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2857,6 +3372,11 @@
           <t>Occupational Diseases</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2881,6 +3401,11 @@
           <t>Digestive System and Oral Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2905,6 +3430,11 @@
           <t>Plant Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2929,6 +3459,11 @@
           <t>Integumentary System Physiological Phenomena</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2953,6 +3488,11 @@
           <t>Anesthesia and Analgesia</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2977,6 +3517,11 @@
           <t>Endocrine System</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3001,6 +3546,11 @@
           <t>Bacterial Structures</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3025,6 +3575,11 @@
           <t>Archaea</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3049,6 +3604,11 @@
           <t>Viral Structures</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3073,6 +3633,11 @@
           <t>Fungal Structures</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3095,6 +3660,11 @@
       <c r="F114" t="inlineStr">
         <is>
           <t>Disorders of Environmental Origin</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
